--- a/www/flightdata/xlsx/eoss-364.xlsx
+++ b/www/flightdata/xlsx/eoss-364.xlsx
@@ -2532,7 +2532,7 @@
         <v>25754.99</v>
       </c>
       <c r="I2">
-        <v>445</v>
+        <v>285</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
